--- a/artfynd/A 59808-2024 artfynd.xlsx
+++ b/artfynd/A 59808-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74602946</v>
       </c>
       <c r="B2" t="n">
-        <v>95516</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97459</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>453644.2286465614</v>
+        <v>453644</v>
       </c>
       <c r="R2" t="n">
-        <v>6356201.48437255</v>
+        <v>6356201</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1991-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1991-01-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">

--- a/artfynd/A 59808-2024 artfynd.xlsx
+++ b/artfynd/A 59808-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74602946</v>
       </c>
       <c r="B2" t="n">
-        <v>97459</v>
+        <v>97460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59808-2024 artfynd.xlsx
+++ b/artfynd/A 59808-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74602946</v>
       </c>
       <c r="B2" t="n">
-        <v>97460</v>
+        <v>97487</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59808-2024 artfynd.xlsx
+++ b/artfynd/A 59808-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74602946</v>
       </c>
       <c r="B2" t="n">
-        <v>97487</v>
+        <v>97493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59808-2024 artfynd.xlsx
+++ b/artfynd/A 59808-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74602946</v>
       </c>
       <c r="B2" t="n">
-        <v>97493</v>
+        <v>97500</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59808-2024 artfynd.xlsx
+++ b/artfynd/A 59808-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74602946</v>
       </c>
       <c r="B2" t="n">
-        <v>97500</v>
+        <v>97504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59808-2024 artfynd.xlsx
+++ b/artfynd/A 59808-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74602946</v>
       </c>
       <c r="B2" t="n">
-        <v>97504</v>
+        <v>97511</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59808-2024 artfynd.xlsx
+++ b/artfynd/A 59808-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74602946</v>
       </c>
       <c r="B2" t="n">
-        <v>97514</v>
+        <v>97519</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59808-2024 artfynd.xlsx
+++ b/artfynd/A 59808-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74602946</v>
       </c>
       <c r="B2" t="n">
-        <v>97519</v>
+        <v>97527</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 59808-2024 artfynd.xlsx
+++ b/artfynd/A 59808-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74602946</v>
       </c>
       <c r="B2" t="n">
-        <v>97527</v>
+        <v>97537</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
